--- a/GGIS517/assignment4/Book1.xlsx
+++ b/GGIS517/assignment4/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yun-roulin/Documents/GitHub/yunroulin960315.github.io/GGIS517/assignment4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27E84AF-CD11-0B48-9D25-2B035142283C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1368809E-888B-1743-91DA-4596D8CECF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="560" yWindow="920" windowWidth="27640" windowHeight="16660" activeTab="3" xr2:uid="{F35FF6E5-A22D-9C42-A0B9-18CA899E2A77}"/>
+    <workbookView xWindow="14680" yWindow="660" windowWidth="14720" windowHeight="17360" activeTab="3" xr2:uid="{F35FF6E5-A22D-9C42-A0B9-18CA899E2A77}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
